--- a/InputData/trans/BAADTbVT/cn - BAU Avg Annual Dist Traveled by Veh Type.xlsx
+++ b/InputData/trans/BAADTbVT/cn - BAU Avg Annual Dist Traveled by Veh Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BAADTbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4D882F-3644-4D7F-9413-561014E2F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF321F6-78E7-4453-ABC2-762A8A343A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9768" yWindow="475" windowWidth="13218" windowHeight="13314" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6657" yWindow="2500" windowWidth="17660" windowHeight="11289" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="32" r:id="rId1"/>
@@ -872,7 +872,7 @@
     <numFmt numFmtId="181" formatCode="0.0"/>
     <numFmt numFmtId="182" formatCode="0.000_ "/>
     <numFmt numFmtId="183" formatCode="0_ "/>
-    <numFmt numFmtId="188" formatCode="0.00_ "/>
+    <numFmt numFmtId="184" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="58">
     <font>
@@ -2009,6 +2009,9 @@
     <xf numFmtId="180" fontId="45" fillId="32" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="184" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2016,10 +2019,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2030,12 +2036,6 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="154">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4265,7 +4265,7 @@
         <v>832489.27135522617</v>
       </c>
       <c r="H4" s="6">
-        <f t="shared" ref="H4:AQ6" si="2">$B4</f>
+        <f t="shared" ref="H4:AQ4" si="2">$B4</f>
         <v>832489.27135522617</v>
       </c>
       <c r="I4" s="6">
@@ -5263,23 +5263,23 @@
         <v>36306.934435591582</v>
       </c>
       <c r="D3" s="6">
-        <f t="shared" ref="D3:AQ3" si="1">C3</f>
+        <f>B3</f>
         <v>36306.934435591582</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" si="1"/>
+        <f>B3</f>
         <v>36306.934435591582</v>
       </c>
       <c r="F3" s="6">
-        <f t="shared" si="1"/>
+        <f>B3</f>
         <v>36306.934435591582</v>
       </c>
       <c r="G3" s="6">
-        <f t="shared" si="1"/>
+        <f>B3</f>
         <v>36306.934435591582</v>
       </c>
       <c r="H3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D3:AQ3" si="1">G3</f>
         <v>36306.934435591582</v>
       </c>
       <c r="I3" s="6">
@@ -5427,27 +5427,27 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="52">
+      <c r="B4" s="44">
         <f>aircraft!E32</f>
         <v>3203383.8434537211</v>
       </c>
-      <c r="C4" s="52">
+      <c r="C4" s="44">
         <f>aircraft!F32</f>
         <v>3203297.8908665339</v>
       </c>
-      <c r="D4" s="52">
+      <c r="D4" s="44">
         <f>aircraft!G32</f>
         <v>3484710.9203222673</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="44">
         <f>aircraft!H32</f>
         <v>2826422.4300539652</v>
       </c>
-      <c r="F4" s="52">
+      <c r="F4" s="44">
         <f>aircraft!I32</f>
         <v>2737417.24134245</v>
       </c>
-      <c r="G4" s="52">
+      <c r="G4" s="44">
         <f>aircraft!J32</f>
         <v>3275448.4268608387</v>
       </c>
@@ -5951,7 +5951,7 @@
         <v>3728.3290871807621</v>
       </c>
       <c r="C7" s="6">
-        <f t="shared" ref="C6:R7" si="5">$B7</f>
+        <f t="shared" ref="C7" si="5">$B7</f>
         <v>3728.3290871807621</v>
       </c>
       <c r="D7" s="6">
@@ -6229,17 +6229,17 @@
       <c r="G6" s="18"/>
     </row>
     <row r="15" spans="1:24">
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="47"/>
+      <c r="D15" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="45" t="s">
+      <c r="F15" s="48" t="s">
         <v>129</v>
       </c>
     </row>
@@ -6250,9 +6250,9 @@
       <c r="C16" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
       <c r="H16">
         <v>2019</v>
       </c>
@@ -6451,14 +6451,14 @@
       <c r="A19" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="47">
         <v>8857.1</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44">
+      <c r="D19" s="47"/>
+      <c r="E19" s="47">
         <v>59636.4</v>
       </c>
-      <c r="F19" s="44"/>
+      <c r="F19" s="47"/>
       <c r="H19" t="s">
         <v>152</v>
       </c>
@@ -6585,16 +6585,16 @@
       <c r="A21" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="44">
+      <c r="C21" s="47">
         <f>(C17*C18*C20+D17*D18*D20)/10^8</f>
         <v>376369.43672413111</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44">
+      <c r="D21" s="47"/>
+      <c r="E21" s="47">
         <f>(E17*E18*E20+F17*F18*F20)/10^8</f>
         <v>59669.457850799998</v>
       </c>
-      <c r="F21" s="44"/>
+      <c r="F21" s="47"/>
       <c r="H21" t="s">
         <v>154</v>
       </c>
@@ -6651,11 +6651,11 @@
       <c r="A22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="47">
         <f>(11800*B17+44400*1702+96000*2858281)/(B17+1702+2858281)</f>
         <v>53897.172393579589</v>
       </c>
-      <c r="C22" s="44"/>
+      <c r="C22" s="47"/>
       <c r="D22">
         <v>50000</v>
       </c>
@@ -6723,11 +6723,11 @@
       <c r="A23" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="47">
         <f>B22/converter!$D$2/2.95</f>
         <v>11352.903703490325</v>
       </c>
-      <c r="C23" s="44"/>
+      <c r="C23" s="47"/>
       <c r="D23">
         <f>D22/converter!$D$2</f>
         <v>31069.409059839683</v>
@@ -7255,30 +7255,30 @@
       </c>
     </row>
     <row r="25" spans="2:11">
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="44">
         <f>D24/converter!$D$2</f>
         <v>16430.842393390882</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="44">
         <f>E24/converter!$D$2*$J$25</f>
         <v>16430.860300226996</v>
       </c>
-      <c r="F25" s="52">
+      <c r="F25" s="44">
         <f>F24/converter!$D$2*$J$25</f>
         <v>18548.431401273247</v>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="44">
         <f>G24/converter!$D$2*$J$25</f>
         <v>12923.217202246135</v>
       </c>
-      <c r="H25" s="52">
+      <c r="H25" s="44">
         <f>H24/converter!$D$2*$J$25</f>
         <v>28566.832019599085</v>
       </c>
-      <c r="I25" s="52">
+      <c r="I25" s="44">
         <f>I24/converter!$D$2*$J$25</f>
         <v>29512.097226889557</v>
       </c>
@@ -7290,30 +7290,30 @@
       </c>
     </row>
     <row r="26" spans="2:11">
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="44">
         <f>D23/$D$23</f>
         <v>1</v>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="44">
         <f>E23/$D$23</f>
         <v>0.56207417078046595</v>
       </c>
-      <c r="F26" s="52">
+      <c r="F26" s="44">
         <f t="shared" ref="F26:I26" si="2">F23/$D$23</f>
         <v>0.65057865176179397</v>
       </c>
-      <c r="G26" s="52">
+      <c r="G26" s="44">
         <f t="shared" si="2"/>
         <v>0.44724817428909469</v>
       </c>
-      <c r="H26" s="52">
+      <c r="H26" s="44">
         <f t="shared" si="2"/>
         <v>1.0015503243441719</v>
       </c>
-      <c r="I26" s="52">
+      <c r="I26" s="44">
         <f t="shared" si="2"/>
         <v>1.0742863748249085</v>
       </c>
@@ -7410,30 +7410,30 @@
       </c>
     </row>
     <row r="30" spans="2:11">
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="44">
         <f>D29/converter!$D$2</f>
         <v>522.14192500125102</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="44">
         <f>E29/converter!$D$2*$J$30</f>
         <v>522.46559899225224</v>
       </c>
-      <c r="F30" s="52">
+      <c r="F30" s="44">
         <f>F29/converter!$D$2*$J$30</f>
         <v>537.80613637083309</v>
       </c>
-      <c r="G30" s="52">
+      <c r="G30" s="44">
         <f>G29/converter!$D$2*$J$30</f>
         <v>563.80716782872753</v>
       </c>
-      <c r="H30" s="52">
+      <c r="H30" s="44">
         <f>H29/converter!$D$2*$J$30</f>
         <v>566.16351581496099</v>
       </c>
-      <c r="I30" s="52">
+      <c r="I30" s="44">
         <f>I29/converter!$D$2*$J$30</f>
         <v>550.41485804107867</v>
       </c>
@@ -7442,30 +7442,30 @@
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="44">
         <f>D28/$D$28</f>
         <v>1</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="44">
         <f t="shared" ref="E31:I31" si="5">E28/$D$28</f>
         <v>1.011016499900603</v>
       </c>
-      <c r="F31" s="52">
+      <c r="F31" s="44">
         <f t="shared" si="5"/>
         <v>1.1012524020939634</v>
       </c>
-      <c r="G31" s="52">
+      <c r="G31" s="44">
         <f t="shared" si="5"/>
         <v>1.1909648134649791</v>
       </c>
-      <c r="H31" s="52">
+      <c r="H31" s="44">
         <f t="shared" si="5"/>
         <v>1.2080180239878073</v>
       </c>
-      <c r="I31" s="52">
+      <c r="I31" s="44">
         <f t="shared" si="5"/>
         <v>1.1881883241667219</v>
       </c>
@@ -7513,7 +7513,7 @@
       <c r="F8" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="45">
         <v>239.70073166222036</v>
       </c>
       <c r="H8">
@@ -7684,59 +7684,59 @@
       </c>
     </row>
     <row r="27" spans="3:11">
-      <c r="D27" s="52" t="s">
+      <c r="D27" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="44">
         <f>E26/converter!$D$2</f>
         <v>832489.27135522617</v>
       </c>
-      <c r="F27" s="52">
+      <c r="F27" s="44">
         <f>(F26/converter!$D$2)*1.8912417621456</f>
         <v>832466.83716849552</v>
       </c>
-      <c r="G27" s="52">
+      <c r="G27" s="44">
         <f>(G26/converter!$D$2)*1.8912417621456</f>
         <v>830227.05473397288</v>
       </c>
-      <c r="H27" s="52">
+      <c r="H27" s="44">
         <f>(H26/converter!$D$2)*1.8912417621456</f>
         <v>486781.18511336844</v>
       </c>
-      <c r="I27" s="52">
+      <c r="I27" s="44">
         <f>(I26/converter!$D$2)*1.8912417621456</f>
         <v>1259470.6699362323</v>
       </c>
-      <c r="J27" s="52">
+      <c r="J27" s="44">
         <f>J26/converter!$D$2</f>
         <v>811425.64173001947</v>
       </c>
     </row>
     <row r="28" spans="3:11">
-      <c r="D28" s="52" t="s">
+      <c r="D28" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="44">
         <f>E26/$E$26</f>
         <v>1</v>
       </c>
-      <c r="F28" s="52">
+      <c r="F28" s="44">
         <f t="shared" ref="F28:J28" si="1">F26/$E$26</f>
         <v>0.52873888029323191</v>
       </c>
-      <c r="G28" s="52">
+      <c r="G28" s="44">
         <f t="shared" si="1"/>
         <v>0.52731628902153871</v>
       </c>
-      <c r="H28" s="52">
+      <c r="H28" s="44">
         <f t="shared" si="1"/>
         <v>0.30917764801309411</v>
       </c>
-      <c r="I28" s="52">
+      <c r="I28" s="44">
         <f t="shared" si="1"/>
         <v>0.79994911755200926</v>
       </c>
-      <c r="J28" s="52">
+      <c r="J28" s="44">
         <f t="shared" si="1"/>
         <v>0.97469801671928236</v>
       </c>
@@ -7820,59 +7820,59 @@
       </c>
     </row>
     <row r="32" spans="3:11">
-      <c r="D32" s="52" t="s">
+      <c r="D32" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="E32" s="52">
+      <c r="E32" s="44">
         <f>E31/converter!$D$2</f>
         <v>3203383.8434537211</v>
       </c>
-      <c r="F32" s="52">
+      <c r="F32" s="44">
         <f>(F31/converter!$D$2)*1.17806178963019</f>
         <v>3203297.8908665339</v>
       </c>
-      <c r="G32" s="52">
+      <c r="G32" s="44">
         <f>(G31/converter!$D$2)*1.17806178963019</f>
         <v>3484710.9203222673</v>
       </c>
-      <c r="H32" s="52">
+      <c r="H32" s="44">
         <f>(H31/converter!$D$2)*1.17806178963019</f>
         <v>2826422.4300539652</v>
       </c>
-      <c r="I32" s="52">
+      <c r="I32" s="44">
         <f>(I31/converter!$D$2)*1.17806178963019</f>
         <v>2737417.24134245</v>
       </c>
-      <c r="J32" s="52">
+      <c r="J32" s="44">
         <f>(J31/converter!$D$2)*1.17806178963019</f>
         <v>3275448.4268608387</v>
       </c>
     </row>
     <row r="33" spans="4:10">
-      <c r="D33" s="52" t="s">
+      <c r="D33" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="E33" s="52">
+      <c r="E33" s="44">
         <f>E30/$E$30</f>
         <v>1</v>
       </c>
-      <c r="F33" s="52">
+      <c r="F33" s="44">
         <f t="shared" ref="F33:J33" si="3">F30/$E$30</f>
         <v>0.91261398176291797</v>
       </c>
-      <c r="G33" s="52">
+      <c r="G33" s="44">
         <f t="shared" si="3"/>
         <v>1.0568389057750762</v>
       </c>
-      <c r="H33" s="52">
+      <c r="H33" s="44">
         <f t="shared" si="3"/>
         <v>0.96542553191489366</v>
       </c>
-      <c r="I33" s="52">
+      <c r="I33" s="44">
         <f t="shared" si="3"/>
         <v>1.0775835866261398</v>
       </c>
-      <c r="J33" s="52">
+      <c r="J33" s="44">
         <f t="shared" si="3"/>
         <v>1.3445668693009118</v>
       </c>
@@ -8037,7 +8037,7 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="54">
+      <c r="A22" s="46">
         <v>17.533087393027898</v>
       </c>
       <c r="B22" t="s">
@@ -8123,30 +8123,30 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="52">
+      <c r="D25" s="44">
         <f>D24/converter!$D$2</f>
         <v>48562.432819545516</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="44">
         <f>E24/converter!$D$2*$J$25</f>
         <v>20718.787113966806</v>
       </c>
-      <c r="F25" s="52">
+      <c r="F25" s="44">
         <f>F24/converter!$D$2*$J$25</f>
         <v>20939.711526266026</v>
       </c>
-      <c r="G25" s="52">
+      <c r="G25" s="44">
         <f>G24/converter!$D$2*$J$25</f>
         <v>14767.467510285478</v>
       </c>
-      <c r="H25" s="52">
+      <c r="H25" s="44">
         <f>H24/converter!$D$2*$J$25</f>
         <v>36236.600356332157</v>
       </c>
-      <c r="I25" s="52">
+      <c r="I25" s="44">
         <f>I24/converter!$D$2*$J$25</f>
         <v>39545.748292294891</v>
       </c>
@@ -8155,30 +8155,30 @@
       </c>
     </row>
     <row r="26" spans="1:10">
-      <c r="C26" s="52" t="s">
+      <c r="C26" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="44">
         <f>D24/$D$24</f>
         <v>1</v>
       </c>
-      <c r="E26" s="52">
+      <c r="E26" s="44">
         <f>E23/$D$23</f>
         <v>0.41147132169576056</v>
       </c>
-      <c r="F26" s="52">
+      <c r="F26" s="44">
         <f t="shared" ref="F26:I26" si="2">F23/$D$23</f>
         <v>0.41271820448877805</v>
       </c>
-      <c r="G26" s="52">
+      <c r="G26" s="44">
         <f t="shared" si="2"/>
         <v>0.28179551122194513</v>
       </c>
-      <c r="H26" s="52">
+      <c r="H26" s="44">
         <f t="shared" si="2"/>
         <v>0.67082294264339148</v>
       </c>
-      <c r="I26" s="52">
+      <c r="I26" s="44">
         <f t="shared" si="2"/>
         <v>0.68204488778054861</v>
       </c>
@@ -8270,30 +8270,30 @@
       </c>
     </row>
     <row r="30" spans="1:10">
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="52">
+      <c r="D30" s="44">
         <f>D29/converter!$D$2</f>
         <v>22769.886012460112</v>
       </c>
-      <c r="E30" s="52">
+      <c r="E30" s="44">
         <f>E29/converter!$D$2*$J$30</f>
         <v>22769.630777300627</v>
       </c>
-      <c r="F30" s="52">
+      <c r="F30" s="44">
         <f>F29/converter!$D$2*$J$30</f>
         <v>25055.019492774827</v>
       </c>
-      <c r="G30" s="52">
+      <c r="G30" s="44">
         <f>G29/converter!$D$2*$J$30</f>
         <v>27093.981489833517</v>
       </c>
-      <c r="H30" s="52">
+      <c r="H30" s="44">
         <f>H29/converter!$D$2*$J$30</f>
         <v>29993.366585977961</v>
       </c>
-      <c r="I30" s="52">
+      <c r="I30" s="44">
         <f>I29/converter!$D$2*$J$30</f>
         <v>35035.712842952897</v>
       </c>
@@ -8302,30 +8302,30 @@
       </c>
     </row>
     <row r="31" spans="1:10">
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="52">
+      <c r="D31" s="44">
         <f>D28/$D$28</f>
         <v>1</v>
       </c>
-      <c r="E31" s="52">
+      <c r="E31" s="44">
         <f t="shared" ref="E31:I31" si="5">E28/$D$28</f>
         <v>1.0180006348412416</v>
       </c>
-      <c r="F31" s="52">
+      <c r="F31" s="44">
         <f t="shared" si="5"/>
         <v>1.1117176303107836</v>
       </c>
-      <c r="G31" s="52">
+      <c r="G31" s="44">
         <f t="shared" si="5"/>
         <v>1.1639054278926158</v>
       </c>
-      <c r="H31" s="52">
+      <c r="H31" s="44">
         <f t="shared" si="5"/>
         <v>1.2499783576849457</v>
       </c>
-      <c r="I31" s="52">
+      <c r="I31" s="44">
         <f t="shared" si="5"/>
         <v>1.3603195367582697</v>
       </c>
@@ -10525,81 +10525,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="13.6" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="H1" s="50" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="H1" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
       <c r="N1" s="36"/>
     </row>
     <row r="2" spans="1:21" s="34" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="52" t="s">
         <v>112</v>
       </c>
       <c r="G2" s="11"/>
-      <c r="H2" s="48" t="s">
+      <c r="H2" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="52" t="s">
         <v>115</v>
       </c>
-      <c r="K2" s="48" t="s">
+      <c r="K2" s="52" t="s">
         <v>114</v>
       </c>
-      <c r="L2" s="48" t="s">
+      <c r="L2" s="52" t="s">
         <v>113</v>
       </c>
       <c r="M2" s="35"/>
-      <c r="N2" s="48" t="s">
+      <c r="N2" s="52" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:21" s="34" customFormat="1" ht="13.6" customHeight="1">
-      <c r="A3" s="48"/>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
+      <c r="A3" s="52"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
       <c r="M3" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="N3" s="48"/>
+      <c r="N3" s="52"/>
       <c r="P3" s="34" t="s">
         <v>160</v>
       </c>
@@ -10756,12 +10756,12 @@
       <c r="N6" s="29">
         <v>4.1500000000000004</v>
       </c>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
     </row>
     <row r="7" spans="1:21" ht="13.6" customHeight="1">
       <c r="A7" s="23" t="s">
@@ -10803,18 +10803,18 @@
       <c r="N7" s="29">
         <v>8.18</v>
       </c>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46" t="s">
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="S7" s="46" t="s">
+      <c r="S7" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="T7" s="46" t="s">
+      <c r="T7" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="U7" s="46" t="s">
+      <c r="U7" s="51" t="s">
         <v>112</v>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       <c r="N8" s="29">
         <v>10.1</v>
       </c>
-      <c r="P8" s="46"/>
-      <c r="Q8" s="46"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+      <c r="R8" s="51"/>
+      <c r="S8" s="51"/>
+      <c r="T8" s="51"/>
+      <c r="U8" s="51"/>
     </row>
     <row r="9" spans="1:21" ht="13.6" customHeight="1">
       <c r="A9" s="23" t="s">
@@ -10905,7 +10905,7 @@
       <c r="N9" s="29">
         <v>13.42</v>
       </c>
-      <c r="P9" s="47" t="s">
+      <c r="P9" s="49" t="s">
         <v>109</v>
       </c>
       <c r="Q9" s="33">
@@ -10964,7 +10964,7 @@
       <c r="N10" s="29">
         <v>16.61</v>
       </c>
-      <c r="P10" s="47"/>
+      <c r="P10" s="49"/>
       <c r="Q10" s="33">
         <v>2020</v>
       </c>
@@ -11025,7 +11025,7 @@
       <c r="N11" s="29">
         <v>18.579999999999998</v>
       </c>
-      <c r="P11" s="47"/>
+      <c r="P11" s="49"/>
       <c r="Q11" s="33">
         <v>2021</v>
       </c>
@@ -11086,7 +11086,7 @@
       <c r="N12" s="29">
         <v>22.3</v>
       </c>
-      <c r="P12" s="47"/>
+      <c r="P12" s="49"/>
       <c r="Q12" s="33">
         <v>2022</v>
       </c>
@@ -11147,7 +11147,7 @@
       <c r="N13" s="29">
         <v>24.93</v>
       </c>
-      <c r="P13" s="47" t="s">
+      <c r="P13" s="49" t="s">
         <v>104</v>
       </c>
       <c r="Q13" s="33">
@@ -11206,7 +11206,7 @@
       <c r="N14" s="29">
         <v>29.1</v>
       </c>
-      <c r="P14" s="47"/>
+      <c r="P14" s="49"/>
       <c r="Q14" s="33">
         <v>2020</v>
       </c>
@@ -11267,7 +11267,7 @@
       <c r="N15" s="29">
         <v>33.450000000000003</v>
       </c>
-      <c r="P15" s="47"/>
+      <c r="P15" s="49"/>
       <c r="Q15" s="33">
         <v>2021</v>
       </c>
@@ -11328,7 +11328,7 @@
       <c r="N16" s="29">
         <v>42.34</v>
       </c>
-      <c r="P16" s="47"/>
+      <c r="P16" s="49"/>
       <c r="Q16" s="33">
         <v>2022</v>
       </c>
@@ -11472,14 +11472,14 @@
         <v>51.55</v>
       </c>
       <c r="P19" s="37"/>
-      <c r="Q19" s="47" t="s">
+      <c r="Q19" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
-      <c r="U19" s="47"/>
-      <c r="V19" s="47"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
     </row>
     <row r="20" spans="1:23" ht="13.6" customHeight="1">
       <c r="A20" s="23" t="s">
@@ -11581,10 +11581,10 @@
         <v>71.8</v>
       </c>
       <c r="P21" s="37"/>
-      <c r="Q21" s="46" t="s">
+      <c r="Q21" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="R21" s="46"/>
+      <c r="R21" s="51"/>
       <c r="S21" s="32" cm="1">
         <f t="array" ref="S21:V21">TRANSPOSE(R9:R12)</f>
         <v>1</v>
@@ -11644,10 +11644,10 @@
         <v>78.900000000000006</v>
       </c>
       <c r="P22" s="37"/>
-      <c r="Q22" s="46" t="s">
+      <c r="Q22" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="R22" s="46"/>
+      <c r="R22" s="51"/>
       <c r="S22" s="32">
         <v>1</v>
       </c>
@@ -11709,10 +11709,10 @@
         <v>94.275260000000003</v>
       </c>
       <c r="P23" s="37"/>
-      <c r="Q23" s="46" t="s">
+      <c r="Q23" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="R23" s="46"/>
+      <c r="R23" s="51"/>
       <c r="S23" s="32" cm="1">
         <f t="array" ref="S23:V24">TRANSPOSE(T9:U12)</f>
         <v>1</v>
@@ -11772,10 +11772,10 @@
         <v>116.386674</v>
       </c>
       <c r="P24" s="37"/>
-      <c r="Q24" s="46" t="s">
+      <c r="Q24" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="R24" s="46"/>
+      <c r="R24" s="51"/>
       <c r="S24" s="32">
         <v>1</v>
       </c>
@@ -11833,14 +11833,14 @@
       <c r="N25" s="29">
         <v>119.602272</v>
       </c>
-      <c r="Q25" s="47" t="s">
+      <c r="Q25" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="R25" s="47"/>
-      <c r="S25" s="47"/>
-      <c r="T25" s="47"/>
-      <c r="U25" s="47"/>
-      <c r="V25" s="47"/>
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="49"/>
+      <c r="V25" s="49"/>
     </row>
     <row r="26" spans="1:23" ht="13.6" customHeight="1">
       <c r="A26" s="23">
@@ -11935,10 +11935,10 @@
       <c r="N27" s="29">
         <v>178.89815999999999</v>
       </c>
-      <c r="Q27" s="46" t="s">
+      <c r="Q27" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="R27" s="46"/>
+      <c r="R27" s="51"/>
       <c r="S27" s="32" cm="1">
         <f t="array" ref="S27:V30">TRANSPOSE(R13:U16)</f>
         <v>1</v>
@@ -11993,10 +11993,10 @@
       <c r="N28" s="29">
         <v>173.91</v>
       </c>
-      <c r="Q28" s="46" t="s">
+      <c r="Q28" s="51" t="s">
         <v>114</v>
       </c>
-      <c r="R28" s="46"/>
+      <c r="R28" s="51"/>
       <c r="S28" s="32">
         <v>1</v>
       </c>
@@ -12050,10 +12050,10 @@
       <c r="N29" s="29">
         <v>163.88936200000001</v>
       </c>
-      <c r="Q29" s="46" t="s">
+      <c r="Q29" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="R29" s="46"/>
+      <c r="R29" s="51"/>
       <c r="S29" s="32">
         <v>1</v>
       </c>
@@ -12107,10 +12107,10 @@
       <c r="N30" s="29">
         <v>170.29181</v>
       </c>
-      <c r="Q30" s="46" t="s">
+      <c r="Q30" s="51" t="s">
         <v>112</v>
       </c>
-      <c r="R30" s="46"/>
+      <c r="R30" s="51"/>
       <c r="S30" s="32">
         <v>1</v>
       </c>
@@ -12712,14 +12712,16 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="P9:P12"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q19:V19"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="N2:N3"/>
@@ -12734,16 +12736,14 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q25:V25"/>
+    <mergeCell ref="P9:P12"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
   </mergeCells>
   <phoneticPr fontId="42" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12752,15 +12752,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12994,6 +12985,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13004,24 +13004,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F56819-4DDA-43FB-95AC-4A54822EFF7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE52FE69-6D5E-4B98-8743-EF2FB207525C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13041,6 +13023,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F56819-4DDA-43FB-95AC-4A54822EFF7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="a06c533b-533a-4f75-b7db-110f073002e4"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E582446-72E7-41AC-B806-D74F68911B8C}">
   <ds:schemaRefs>

--- a/InputData/trans/BAADTbVT/cn - BAU Avg Annual Dist Traveled by Veh Type.xlsx
+++ b/InputData/trans/BAADTbVT/cn - BAU Avg Annual Dist Traveled by Veh Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BAADTbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF321F6-78E7-4453-ABC2-762A8A343A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10EA5B1-BC41-4481-8941-BE7116CC67E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6657" yWindow="2500" windowWidth="17660" windowHeight="11289" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6711" yWindow="910" windowWidth="17660" windowHeight="11289" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="32" r:id="rId1"/>
@@ -3899,168 +3899,168 @@
         <v>11352.903703490325</v>
       </c>
       <c r="C2" s="38">
-        <f>$B2*'raw data'!T$22</f>
-        <v>9876.7937868592198</v>
+        <f>$B2*'raw data'!T$22*0.98</f>
+        <v>9679.2579111220348</v>
       </c>
       <c r="D2" s="38">
-        <f>$B2*'raw data'!U$22</f>
-        <v>10225.790534907886</v>
+        <f>$B2*'raw data'!U$22*0.98</f>
+        <v>10021.274724209728</v>
       </c>
       <c r="E2" s="38">
         <f>$B2*'raw data'!V$22</f>
         <v>8949.5093804790322</v>
       </c>
       <c r="F2" s="38">
-        <f>$B2*'raw data'!W$22</f>
-        <v>9102.4916173008914</v>
+        <f>$B2*'raw data'!C52</f>
+        <v>10084.243460644011</v>
       </c>
       <c r="G2" s="6">
-        <f>F2</f>
-        <v>9102.4916173008914</v>
+        <f>F2*0.98</f>
+        <v>9882.5585914311305</v>
       </c>
       <c r="H2" s="6">
-        <f>G2</f>
-        <v>9102.4916173008914</v>
+        <f>F2*0.98</f>
+        <v>9882.5585914311305</v>
       </c>
       <c r="I2" s="6">
-        <f t="shared" ref="I2:AQ2" si="0">H2</f>
-        <v>9102.4916173008914</v>
+        <f>H2</f>
+        <v>9882.5585914311305</v>
       </c>
       <c r="J2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" ref="J2:X2" si="0">I2</f>
+        <v>9882.5585914311305</v>
       </c>
       <c r="K2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="L2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="M2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="N2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="O2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="P2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="Q2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="R2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="S2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="T2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="U2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="V2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="W2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="X2" s="6">
         <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <v>9882.5585914311305</v>
       </c>
       <c r="Y2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" ref="H2:AQ2" si="1">X2</f>
+        <v>9882.5585914311305</v>
       </c>
       <c r="Z2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AA2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AB2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AC2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AD2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AE2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AF2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AG2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AH2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AI2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AJ2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AK2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AL2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AM2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AN2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AO2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AP2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
       <c r="AQ2" s="6">
-        <f t="shared" si="0"/>
-        <v>9102.4916173008914</v>
+        <f t="shared" si="1"/>
+        <v>9882.5585914311305</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -4092,147 +4092,147 @@
         <v>24910.722658092891</v>
       </c>
       <c r="H3" s="6">
-        <f t="shared" ref="H3:AQ3" si="1">G3</f>
+        <f t="shared" ref="H3:AQ3" si="2">G3</f>
         <v>24910.722658092891</v>
       </c>
       <c r="I3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="J3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="K3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="L3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="M3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="N3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="O3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="P3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="R3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="S3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="T3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="U3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="V3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="W3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="X3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="Y3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="Z3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AA3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AB3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AC3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AD3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AE3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AF3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AG3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AH3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AI3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AJ3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AK3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AL3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AM3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AN3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AO3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AP3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
       <c r="AQ3" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24910.722658092891</v>
       </c>
     </row>
@@ -4265,147 +4265,147 @@
         <v>832489.27135522617</v>
       </c>
       <c r="H4" s="6">
-        <f t="shared" ref="H4:AQ4" si="2">$B4</f>
+        <f t="shared" ref="H4:AQ4" si="3">$B4</f>
         <v>832489.27135522617</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="J4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="L4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="N4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="O4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="P4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="R4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="S4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="T4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="U4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="W4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="X4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="Y4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="Z4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AA4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AB4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AC4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AD4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AE4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AF4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AG4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AH4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AI4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AJ4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AK4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AL4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AM4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AN4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AO4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AP4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
       <c r="AQ4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>832489.27135522617</v>
       </c>
     </row>
@@ -4442,143 +4442,143 @@
         <v>29512.097226889557</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" ref="I5:AQ5" si="3">H5</f>
+        <f t="shared" ref="I5:AQ5" si="4">H5</f>
         <v>29512.097226889557</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="O5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="P5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="R5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="S5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="T5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="U5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="V5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="W5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="X5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="Y5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="Z5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AA5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AB5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AC5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AD5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AE5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AF5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AG5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AH5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AI5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AJ5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AK5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AL5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AM5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AN5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AO5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AP5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
       <c r="AQ5" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29512.097226889557</v>
       </c>
     </row>
@@ -4615,143 +4615,143 @@
         <v>39545.748292294891</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" ref="I6:AQ6" si="4">$G6</f>
+        <f t="shared" ref="I6:AQ6" si="5">$G6</f>
         <v>39545.748292294891</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="N6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="O6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="P6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="R6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="S6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="T6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="W6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="Y6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AI6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AJ6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AK6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AL6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AM6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AN6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AO6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AP6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
       <c r="AQ6" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>39545.748292294891</v>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
         <v>36306.934435591582</v>
       </c>
       <c r="H3" s="6">
-        <f t="shared" ref="D3:AQ3" si="1">G3</f>
+        <f t="shared" ref="H3:AQ3" si="1">G3</f>
         <v>36306.934435591582</v>
       </c>
       <c r="I3" s="6">
